--- a/Opening_Closing_Stock_Data_2021_2025.xlsx
+++ b/Opening_Closing_Stock_Data_2021_2025.xlsx
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="34">
+  <si>
+    <t>Equity (Stocks)</t>
+  </si>
   <si>
     <t>Asset</t>
   </si>
@@ -89,18 +92,30 @@
     <t>HDFC Bank</t>
   </si>
   <si>
+    <t>Exchange Traded Funds (ETFs)</t>
+  </si>
+  <si>
     <t>Gold BeES (ETF)</t>
   </si>
   <si>
+    <t>Real Estate Investment Trusts (REITs)</t>
+  </si>
+  <si>
     <t>Embassy Office Parks REIT</t>
   </si>
   <si>
     <t>Mindspace Business Parks REIT</t>
   </si>
   <si>
+    <t>Infrastructure Investment Trust (InvIT)</t>
+  </si>
+  <si>
     <t>IRB InvIT Fund</t>
   </si>
   <si>
+    <t>Fixed Income / Bonds</t>
+  </si>
+  <si>
     <t>India Grid Trust</t>
   </si>
   <si>
@@ -108,6 +123,9 @@
   </si>
   <si>
     <t>NABARD Bond</t>
+  </si>
+  <si>
+    <t>Market Index</t>
   </si>
   <si>
     <t>Nifty 50 Index</t>
@@ -123,9 +141,17 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -140,11 +166,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -594,154 +620,167 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1088,7 +1127,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.7777777777778" customWidth="1"/>
@@ -1104,74 +1143,54 @@
     <col min="11" max="11" width="13.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" ht="23.4" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
+      <c r="K2" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="B2">
-        <v>38.6</v>
-      </c>
-      <c r="C2">
-        <v>59.1</v>
-      </c>
-      <c r="D2">
-        <v>59.5</v>
-      </c>
-      <c r="E2">
-        <v>99.85</v>
-      </c>
-      <c r="F2">
-        <v>100.2</v>
-      </c>
-      <c r="G2">
-        <v>412.75</v>
-      </c>
-      <c r="H2">
-        <v>413.5</v>
-      </c>
-      <c r="I2">
-        <v>589.4</v>
-      </c>
-      <c r="J2">
-        <v>592.1</v>
-      </c>
-      <c r="K2">
-        <v>926.1</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1179,34 +1198,34 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>212.5</v>
+        <v>38.6</v>
       </c>
       <c r="C3">
-        <v>260.3</v>
+        <v>59.1</v>
       </c>
       <c r="D3">
-        <v>261.1</v>
+        <v>59.5</v>
       </c>
       <c r="E3">
-        <v>742.6</v>
+        <v>99.85</v>
       </c>
       <c r="F3">
-        <v>745</v>
+        <v>100.2</v>
       </c>
       <c r="G3">
-        <v>2106.85</v>
+        <v>412.75</v>
       </c>
       <c r="H3">
-        <v>2112.4</v>
+        <v>413.5</v>
       </c>
       <c r="I3">
-        <v>4329.1</v>
+        <v>589.4</v>
       </c>
       <c r="J3">
-        <v>4335.5</v>
+        <v>592.1</v>
       </c>
       <c r="K3">
-        <v>4279</v>
+        <v>926.1</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1214,34 +1233,34 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>124.75</v>
+        <v>212.5</v>
       </c>
       <c r="C4">
-        <v>531.4</v>
+        <v>260.3</v>
       </c>
       <c r="D4">
-        <v>535</v>
+        <v>261.1</v>
       </c>
       <c r="E4">
-        <v>610.25</v>
+        <v>742.6</v>
       </c>
       <c r="F4">
-        <v>612.5</v>
+        <v>745</v>
       </c>
       <c r="G4">
-        <v>1283.4</v>
+        <v>2106.85</v>
       </c>
       <c r="H4">
-        <v>1285</v>
+        <v>2112.4</v>
       </c>
       <c r="I4">
-        <v>1263.15</v>
+        <v>4329.1</v>
       </c>
       <c r="J4">
-        <v>1265.4</v>
+        <v>4335.5</v>
       </c>
       <c r="K4">
-        <v>1045.8</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1249,34 +1268,34 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>652.8</v>
+        <v>124.75</v>
       </c>
       <c r="C5">
-        <v>1030.7</v>
+        <v>531.4</v>
       </c>
       <c r="D5">
-        <v>1035.4</v>
+        <v>535</v>
       </c>
       <c r="E5">
-        <v>1313.25</v>
+        <v>610.25</v>
       </c>
       <c r="F5">
-        <v>1315</v>
+        <v>612.5</v>
       </c>
       <c r="G5">
-        <v>2955.4</v>
+        <v>1283.4</v>
       </c>
       <c r="H5">
-        <v>2962</v>
+        <v>1285</v>
       </c>
       <c r="I5">
-        <v>8348.15</v>
+        <v>1263.15</v>
       </c>
       <c r="J5">
-        <v>8355</v>
+        <v>1265.4</v>
       </c>
       <c r="K5">
-        <v>5051.4</v>
+        <v>1045.8</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1284,34 +1303,34 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>1515.2</v>
+        <v>652.8</v>
       </c>
       <c r="C6">
-        <v>4909.15</v>
+        <v>1030.7</v>
       </c>
       <c r="D6">
-        <v>4925</v>
+        <v>1035.4</v>
       </c>
       <c r="E6">
-        <v>4009.65</v>
+        <v>1313.25</v>
       </c>
       <c r="F6">
-        <v>4015</v>
+        <v>1315</v>
       </c>
       <c r="G6">
-        <v>7433.8</v>
+        <v>2955.4</v>
       </c>
       <c r="H6">
-        <v>7450</v>
+        <v>2962</v>
       </c>
       <c r="I6">
-        <v>11470.25</v>
+        <v>8348.15</v>
       </c>
       <c r="J6">
-        <v>11485</v>
+        <v>8355</v>
       </c>
       <c r="K6">
-        <v>11171.3</v>
+        <v>5051.4</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1319,34 +1338,34 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>584.1</v>
+        <v>1515.2</v>
       </c>
       <c r="C7">
-        <v>831.95</v>
+        <v>4909.15</v>
       </c>
       <c r="D7">
-        <v>835</v>
+        <v>4925</v>
       </c>
       <c r="E7">
-        <v>1258.4</v>
+        <v>4009.65</v>
       </c>
       <c r="F7">
-        <v>1262.1</v>
+        <v>4015</v>
       </c>
       <c r="G7">
-        <v>1834.75</v>
+        <v>7433.8</v>
       </c>
       <c r="H7">
-        <v>1838</v>
+        <v>7450</v>
       </c>
       <c r="I7">
-        <v>3530.15</v>
+        <v>11470.25</v>
       </c>
       <c r="J7">
-        <v>3535.4</v>
+        <v>11485</v>
       </c>
       <c r="K7">
-        <v>4052.1</v>
+        <v>11171.3</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1354,34 +1373,34 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>1987.4</v>
+        <v>584.1</v>
       </c>
       <c r="C8">
-        <v>2368.15</v>
+        <v>831.95</v>
       </c>
       <c r="D8">
-        <v>2370</v>
+        <v>835</v>
       </c>
       <c r="E8">
-        <v>2547.2</v>
+        <v>1258.4</v>
       </c>
       <c r="F8">
-        <v>2551.1</v>
+        <v>1262.1</v>
       </c>
       <c r="G8">
-        <v>2584.95</v>
+        <v>1834.75</v>
       </c>
       <c r="H8">
-        <v>2590</v>
+        <v>1838</v>
       </c>
       <c r="I8">
-        <v>2414.7</v>
+        <v>3530.15</v>
       </c>
       <c r="J8">
-        <v>2420.1</v>
+        <v>3535.4</v>
       </c>
       <c r="K8">
-        <v>3115.8</v>
+        <v>4052.1</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1389,34 +1408,34 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>2902</v>
+        <v>1987.4</v>
       </c>
       <c r="C9">
-        <v>3738.35</v>
+        <v>2368.15</v>
       </c>
       <c r="D9">
-        <v>3745</v>
+        <v>2370</v>
       </c>
       <c r="E9">
-        <v>3256.7</v>
+        <v>2547.2</v>
       </c>
       <c r="F9">
-        <v>3260</v>
+        <v>2551.1</v>
       </c>
       <c r="G9">
-        <v>3793.4</v>
+        <v>2584.95</v>
       </c>
       <c r="H9">
-        <v>3805</v>
+        <v>2590</v>
       </c>
       <c r="I9">
-        <v>4445.6</v>
+        <v>2414.7</v>
       </c>
       <c r="J9">
-        <v>4450</v>
+        <v>2420.1</v>
       </c>
       <c r="K9">
-        <v>3911.35</v>
+        <v>3115.8</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1424,34 +1443,34 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>1428.6</v>
+        <v>2902</v>
       </c>
       <c r="C10">
-        <v>1479.4</v>
+        <v>3738.35</v>
       </c>
       <c r="D10">
-        <v>1482</v>
+        <v>3745</v>
       </c>
       <c r="E10">
-        <v>1628.15</v>
+        <v>3256.7</v>
       </c>
       <c r="F10">
-        <v>1632.1</v>
+        <v>3260</v>
       </c>
       <c r="G10">
-        <v>1709.25</v>
+        <v>3793.4</v>
       </c>
       <c r="H10">
-        <v>1712.5</v>
+        <v>3805</v>
       </c>
       <c r="I10">
-        <v>1861.35</v>
+        <v>4445.6</v>
       </c>
       <c r="J10">
-        <v>1865</v>
+        <v>4450</v>
       </c>
       <c r="K10">
-        <v>2116.45</v>
+        <v>3911.35</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1459,282 +1478,575 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>41.2</v>
+        <v>1428.6</v>
       </c>
       <c r="C11">
-        <v>39.08</v>
+        <v>1479.4</v>
       </c>
       <c r="D11">
-        <v>39.15</v>
+        <v>1482</v>
       </c>
       <c r="E11">
-        <v>44.05</v>
+        <v>1628.15</v>
       </c>
       <c r="F11">
-        <v>44.12</v>
+        <v>1632.1</v>
       </c>
       <c r="G11">
-        <v>50.45</v>
+        <v>1709.25</v>
       </c>
       <c r="H11">
-        <v>50.6</v>
+        <v>1712.5</v>
       </c>
       <c r="I11">
-        <v>60.48</v>
+        <v>1861.35</v>
       </c>
       <c r="J11">
-        <v>60.75</v>
+        <v>1865</v>
       </c>
       <c r="K11">
-        <v>103.95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
+        <v>2116.45</v>
+      </c>
+    </row>
+    <row r="12" ht="23.4" spans="1:11">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12">
-        <v>350.57</v>
-      </c>
-      <c r="C12">
-        <v>339.58</v>
-      </c>
-      <c r="D12">
-        <v>339.7</v>
-      </c>
-      <c r="E12">
-        <v>336.56</v>
-      </c>
-      <c r="F12">
-        <v>337.19</v>
-      </c>
-      <c r="G12">
-        <v>325.06</v>
-      </c>
-      <c r="H12">
-        <v>327.01</v>
-      </c>
-      <c r="I12">
-        <v>369.59</v>
-      </c>
-      <c r="J12">
-        <v>370.92</v>
-      </c>
-      <c r="K12">
-        <v>435.52</v>
-      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13">
-        <v>327.53</v>
-      </c>
-      <c r="C13">
-        <v>327.44</v>
-      </c>
-      <c r="D13">
-        <v>328.74</v>
-      </c>
-      <c r="E13">
-        <v>334.99</v>
-      </c>
-      <c r="F13">
-        <v>338.99</v>
-      </c>
-      <c r="G13">
-        <v>322.35</v>
-      </c>
-      <c r="H13">
-        <v>321.75</v>
-      </c>
-      <c r="I13">
-        <v>363.02</v>
-      </c>
-      <c r="J13">
-        <v>361.34</v>
-      </c>
-      <c r="K13">
-        <v>481.2</v>
+      <c r="A13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14">
+        <v>41.2</v>
+      </c>
+      <c r="C14">
+        <v>39.08</v>
+      </c>
+      <c r="D14">
+        <v>39.15</v>
+      </c>
+      <c r="E14">
+        <v>44.05</v>
+      </c>
+      <c r="F14">
+        <v>44.12</v>
+      </c>
+      <c r="G14">
+        <v>50.45</v>
+      </c>
+      <c r="H14">
+        <v>50.6</v>
+      </c>
+      <c r="I14">
+        <v>60.48</v>
+      </c>
+      <c r="J14">
+        <v>60.75</v>
+      </c>
+      <c r="K14">
+        <v>103.95</v>
+      </c>
+    </row>
+    <row r="15" ht="23.4" spans="1:11">
+      <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14">
-        <v>42.01</v>
-      </c>
-      <c r="C14">
-        <v>54.97</v>
-      </c>
-      <c r="D14">
-        <v>55.68</v>
-      </c>
-      <c r="E14">
-        <v>66.04</v>
-      </c>
-      <c r="F14">
-        <v>66.91</v>
-      </c>
-      <c r="G14">
-        <v>69.06</v>
-      </c>
-      <c r="H14">
-        <v>69.61</v>
-      </c>
-      <c r="I14">
-        <v>60</v>
-      </c>
-      <c r="J14">
-        <v>60.23</v>
-      </c>
-      <c r="K14">
-        <v>62.21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15">
-        <v>117.57</v>
-      </c>
-      <c r="C15">
-        <v>146.04</v>
-      </c>
-      <c r="D15">
-        <v>147.46</v>
-      </c>
-      <c r="E15">
-        <v>139.99</v>
-      </c>
-      <c r="F15">
-        <v>141.49</v>
-      </c>
-      <c r="G15">
-        <v>129.63</v>
-      </c>
-      <c r="H15">
-        <v>130.6</v>
-      </c>
-      <c r="I15">
-        <v>143.05</v>
-      </c>
-      <c r="J15">
-        <v>143.05</v>
-      </c>
-      <c r="K15">
-        <v>166.25</v>
-      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16">
-        <v>1205</v>
-      </c>
-      <c r="C16">
-        <v>1248</v>
-      </c>
-      <c r="D16">
-        <v>1245</v>
-      </c>
-      <c r="E16">
-        <v>1180</v>
-      </c>
-      <c r="F16">
-        <v>1175</v>
-      </c>
-      <c r="G16">
-        <v>1120</v>
-      </c>
-      <c r="H16">
-        <v>1118</v>
-      </c>
-      <c r="I16">
-        <v>1095</v>
-      </c>
-      <c r="J16">
-        <v>1092</v>
-      </c>
-      <c r="K16">
-        <v>1105</v>
+      <c r="A16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17">
-        <v>1085</v>
+        <v>350.57</v>
       </c>
       <c r="C17">
-        <v>1120</v>
+        <v>339.58</v>
       </c>
       <c r="D17">
-        <v>1118</v>
+        <v>339.7</v>
       </c>
       <c r="E17">
-        <v>1065</v>
+        <v>336.56</v>
       </c>
       <c r="F17">
-        <v>1060</v>
+        <v>337.19</v>
       </c>
       <c r="G17">
-        <v>1045</v>
+        <v>325.06</v>
       </c>
       <c r="H17">
-        <v>1048</v>
+        <v>327.01</v>
       </c>
       <c r="I17">
-        <v>1145</v>
+        <v>369.59</v>
       </c>
       <c r="J17">
-        <v>1150</v>
+        <v>370.92</v>
       </c>
       <c r="K17">
-        <v>1165</v>
+        <v>435.52</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18">
+        <v>327.53</v>
+      </c>
+      <c r="C18">
+        <v>327.44</v>
+      </c>
+      <c r="D18">
+        <v>328.74</v>
+      </c>
+      <c r="E18">
+        <v>334.99</v>
+      </c>
+      <c r="F18">
+        <v>338.99</v>
+      </c>
+      <c r="G18">
+        <v>322.35</v>
+      </c>
+      <c r="H18">
+        <v>321.75</v>
+      </c>
+      <c r="I18">
+        <v>363.02</v>
+      </c>
+      <c r="J18">
+        <v>361.34</v>
+      </c>
+      <c r="K18">
+        <v>481.2</v>
+      </c>
+    </row>
+    <row r="19" ht="23.4" spans="1:11">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
         <v>27</v>
       </c>
-      <c r="B18">
+      <c r="B21">
+        <v>42.01</v>
+      </c>
+      <c r="C21">
+        <v>54.97</v>
+      </c>
+      <c r="D21">
+        <v>55.68</v>
+      </c>
+      <c r="E21">
+        <v>66.04</v>
+      </c>
+      <c r="F21">
+        <v>66.91</v>
+      </c>
+      <c r="G21">
+        <v>69.06</v>
+      </c>
+      <c r="H21">
+        <v>69.61</v>
+      </c>
+      <c r="I21">
+        <v>60</v>
+      </c>
+      <c r="J21">
+        <v>60.23</v>
+      </c>
+      <c r="K21">
+        <v>62.21</v>
+      </c>
+    </row>
+    <row r="22" ht="23.4" spans="1:11">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24">
+        <v>117.57</v>
+      </c>
+      <c r="C24">
+        <v>146.04</v>
+      </c>
+      <c r="D24">
+        <v>147.46</v>
+      </c>
+      <c r="E24">
+        <v>139.99</v>
+      </c>
+      <c r="F24">
+        <v>141.49</v>
+      </c>
+      <c r="G24">
+        <v>129.63</v>
+      </c>
+      <c r="H24">
+        <v>130.6</v>
+      </c>
+      <c r="I24">
+        <v>143.05</v>
+      </c>
+      <c r="J24">
+        <v>143.05</v>
+      </c>
+      <c r="K24">
+        <v>166.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25">
+        <v>1205</v>
+      </c>
+      <c r="C25">
+        <v>1248</v>
+      </c>
+      <c r="D25">
+        <v>1245</v>
+      </c>
+      <c r="E25">
+        <v>1180</v>
+      </c>
+      <c r="F25">
+        <v>1175</v>
+      </c>
+      <c r="G25">
+        <v>1120</v>
+      </c>
+      <c r="H25">
+        <v>1118</v>
+      </c>
+      <c r="I25">
+        <v>1095</v>
+      </c>
+      <c r="J25">
+        <v>1092</v>
+      </c>
+      <c r="K25">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26">
+        <v>1085</v>
+      </c>
+      <c r="C26">
+        <v>1120</v>
+      </c>
+      <c r="D26">
+        <v>1118</v>
+      </c>
+      <c r="E26">
+        <v>1065</v>
+      </c>
+      <c r="F26">
+        <v>1060</v>
+      </c>
+      <c r="G26">
+        <v>1045</v>
+      </c>
+      <c r="H26">
+        <v>1048</v>
+      </c>
+      <c r="I26">
+        <v>1145</v>
+      </c>
+      <c r="J26">
+        <v>1150</v>
+      </c>
+      <c r="K26">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="27" ht="23.4" spans="1:11">
+      <c r="A27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29">
         <v>13994</v>
       </c>
-      <c r="C18">
+      <c r="C29">
         <v>17354</v>
       </c>
-      <c r="D18">
+      <c r="D29">
         <v>17387</v>
       </c>
-      <c r="E18">
+      <c r="E29">
         <v>18105</v>
       </c>
-      <c r="F18">
+      <c r="F29">
         <v>18131</v>
       </c>
-      <c r="G18">
+      <c r="G29">
         <v>21731</v>
       </c>
-      <c r="H18">
+      <c r="H29">
         <v>21727</v>
       </c>
-      <c r="I18">
+      <c r="I29">
         <v>23645</v>
       </c>
-      <c r="J18">
+      <c r="J29">
         <v>23600</v>
       </c>
-      <c r="K18">
+      <c r="K29">
         <v>26130</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A27:K27"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/Opening_Closing_Stock_Data_2021_2025.xlsx
+++ b/Opening_Closing_Stock_Data_2021_2025.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8280"/>
   </bookViews>
   <sheets>
     <sheet name="Opening_Closing_Data_2021_2025" sheetId="1" r:id="rId1"/>
@@ -27,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="34">
-  <si>
-    <t>Equity (Stocks)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Asset</t>
   </si>
@@ -92,30 +89,18 @@
     <t>HDFC Bank</t>
   </si>
   <si>
-    <t>Exchange Traded Funds (ETFs)</t>
-  </si>
-  <si>
     <t>Gold BeES (ETF)</t>
   </si>
   <si>
-    <t>Real Estate Investment Trusts (REITs)</t>
-  </si>
-  <si>
     <t>Embassy Office Parks REIT</t>
   </si>
   <si>
     <t>Mindspace Business Parks REIT</t>
   </si>
   <si>
-    <t>Infrastructure Investment Trust (InvIT)</t>
-  </si>
-  <si>
     <t>IRB InvIT Fund</t>
   </si>
   <si>
-    <t>Fixed Income / Bonds</t>
-  </si>
-  <si>
     <t>India Grid Trust</t>
   </si>
   <si>
@@ -123,9 +108,6 @@
   </si>
   <si>
     <t>NABARD Bond</t>
-  </si>
-  <si>
-    <t>Market Index</t>
   </si>
   <si>
     <t>Nifty 50 Index</t>
@@ -141,17 +123,9 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -164,13 +138,6 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -635,152 +602,139 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1127,7 +1081,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.7777777777778" customWidth="1"/>
@@ -1143,54 +1097,74 @@
     <col min="11" max="11" width="13.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.4" spans="1:11">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="3" t="s">
+      <c r="A2" t="s">
         <v>11</v>
+      </c>
+      <c r="B2">
+        <v>38.6</v>
+      </c>
+      <c r="C2">
+        <v>59.1</v>
+      </c>
+      <c r="D2">
+        <v>59.5</v>
+      </c>
+      <c r="E2">
+        <v>99.85</v>
+      </c>
+      <c r="F2">
+        <v>100.2</v>
+      </c>
+      <c r="G2">
+        <v>412.75</v>
+      </c>
+      <c r="H2">
+        <v>413.5</v>
+      </c>
+      <c r="I2">
+        <v>589.4</v>
+      </c>
+      <c r="J2">
+        <v>592.1</v>
+      </c>
+      <c r="K2">
+        <v>926.1</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1198,34 +1172,34 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>38.6</v>
+        <v>212.5</v>
       </c>
       <c r="C3">
-        <v>59.1</v>
+        <v>260.3</v>
       </c>
       <c r="D3">
-        <v>59.5</v>
+        <v>261.1</v>
       </c>
       <c r="E3">
-        <v>99.85</v>
+        <v>742.6</v>
       </c>
       <c r="F3">
-        <v>100.2</v>
+        <v>745</v>
       </c>
       <c r="G3">
-        <v>412.75</v>
+        <v>2106.85</v>
       </c>
       <c r="H3">
-        <v>413.5</v>
+        <v>2112.4</v>
       </c>
       <c r="I3">
-        <v>589.4</v>
+        <v>4329.1</v>
       </c>
       <c r="J3">
-        <v>592.1</v>
+        <v>4335.5</v>
       </c>
       <c r="K3">
-        <v>926.1</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1233,34 +1207,34 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>212.5</v>
+        <v>124.75</v>
       </c>
       <c r="C4">
-        <v>260.3</v>
+        <v>531.4</v>
       </c>
       <c r="D4">
-        <v>261.1</v>
+        <v>535</v>
       </c>
       <c r="E4">
-        <v>742.6</v>
+        <v>610.25</v>
       </c>
       <c r="F4">
-        <v>745</v>
+        <v>612.5</v>
       </c>
       <c r="G4">
-        <v>2106.85</v>
+        <v>1283.4</v>
       </c>
       <c r="H4">
-        <v>2112.4</v>
+        <v>1285</v>
       </c>
       <c r="I4">
-        <v>4329.1</v>
+        <v>1263.15</v>
       </c>
       <c r="J4">
-        <v>4335.5</v>
+        <v>1265.4</v>
       </c>
       <c r="K4">
-        <v>4279</v>
+        <v>1045.8</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1268,34 +1242,34 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>124.75</v>
+        <v>652.8</v>
       </c>
       <c r="C5">
-        <v>531.4</v>
+        <v>1030.7</v>
       </c>
       <c r="D5">
-        <v>535</v>
+        <v>1035.4</v>
       </c>
       <c r="E5">
-        <v>610.25</v>
+        <v>1313.25</v>
       </c>
       <c r="F5">
-        <v>612.5</v>
+        <v>1315</v>
       </c>
       <c r="G5">
-        <v>1283.4</v>
+        <v>2955.4</v>
       </c>
       <c r="H5">
-        <v>1285</v>
+        <v>2962</v>
       </c>
       <c r="I5">
-        <v>1263.15</v>
+        <v>8348.15</v>
       </c>
       <c r="J5">
-        <v>1265.4</v>
+        <v>8355</v>
       </c>
       <c r="K5">
-        <v>1045.8</v>
+        <v>5051.4</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1303,34 +1277,34 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>652.8</v>
+        <v>1515.2</v>
       </c>
       <c r="C6">
-        <v>1030.7</v>
+        <v>4909.15</v>
       </c>
       <c r="D6">
-        <v>1035.4</v>
+        <v>4925</v>
       </c>
       <c r="E6">
-        <v>1313.25</v>
+        <v>4009.65</v>
       </c>
       <c r="F6">
-        <v>1315</v>
+        <v>4015</v>
       </c>
       <c r="G6">
-        <v>2955.4</v>
+        <v>7433.8</v>
       </c>
       <c r="H6">
-        <v>2962</v>
+        <v>7450</v>
       </c>
       <c r="I6">
-        <v>8348.15</v>
+        <v>11470.25</v>
       </c>
       <c r="J6">
-        <v>8355</v>
+        <v>11485</v>
       </c>
       <c r="K6">
-        <v>5051.4</v>
+        <v>11171.3</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1338,34 +1312,34 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>1515.2</v>
+        <v>584.1</v>
       </c>
       <c r="C7">
-        <v>4909.15</v>
+        <v>831.95</v>
       </c>
       <c r="D7">
-        <v>4925</v>
+        <v>835</v>
       </c>
       <c r="E7">
-        <v>4009.65</v>
+        <v>1258.4</v>
       </c>
       <c r="F7">
-        <v>4015</v>
+        <v>1262.1</v>
       </c>
       <c r="G7">
-        <v>7433.8</v>
+        <v>1834.75</v>
       </c>
       <c r="H7">
-        <v>7450</v>
+        <v>1838</v>
       </c>
       <c r="I7">
-        <v>11470.25</v>
+        <v>3530.15</v>
       </c>
       <c r="J7">
-        <v>11485</v>
+        <v>3535.4</v>
       </c>
       <c r="K7">
-        <v>11171.3</v>
+        <v>4052.1</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1373,34 +1347,34 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>584.1</v>
+        <v>1987.4</v>
       </c>
       <c r="C8">
-        <v>831.95</v>
+        <v>2368.15</v>
       </c>
       <c r="D8">
-        <v>835</v>
+        <v>2370</v>
       </c>
       <c r="E8">
-        <v>1258.4</v>
+        <v>2547.2</v>
       </c>
       <c r="F8">
-        <v>1262.1</v>
+        <v>2551.1</v>
       </c>
       <c r="G8">
-        <v>1834.75</v>
+        <v>2584.95</v>
       </c>
       <c r="H8">
-        <v>1838</v>
+        <v>2590</v>
       </c>
       <c r="I8">
-        <v>3530.15</v>
+        <v>2414.7</v>
       </c>
       <c r="J8">
-        <v>3535.4</v>
+        <v>2420.1</v>
       </c>
       <c r="K8">
-        <v>4052.1</v>
+        <v>3115.8</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1408,34 +1382,34 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>1987.4</v>
+        <v>2902</v>
       </c>
       <c r="C9">
-        <v>2368.15</v>
+        <v>3738.35</v>
       </c>
       <c r="D9">
-        <v>2370</v>
+        <v>3745</v>
       </c>
       <c r="E9">
-        <v>2547.2</v>
+        <v>3256.7</v>
       </c>
       <c r="F9">
-        <v>2551.1</v>
+        <v>3260</v>
       </c>
       <c r="G9">
-        <v>2584.95</v>
+        <v>3793.4</v>
       </c>
       <c r="H9">
-        <v>2590</v>
+        <v>3805</v>
       </c>
       <c r="I9">
-        <v>2414.7</v>
+        <v>4445.6</v>
       </c>
       <c r="J9">
-        <v>2420.1</v>
+        <v>4450</v>
       </c>
       <c r="K9">
-        <v>3115.8</v>
+        <v>3911.35</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1443,34 +1417,34 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>2902</v>
+        <v>1428.6</v>
       </c>
       <c r="C10">
-        <v>3738.35</v>
+        <v>1479.4</v>
       </c>
       <c r="D10">
-        <v>3745</v>
+        <v>1482</v>
       </c>
       <c r="E10">
-        <v>3256.7</v>
+        <v>1628.15</v>
       </c>
       <c r="F10">
-        <v>3260</v>
+        <v>1632.1</v>
       </c>
       <c r="G10">
-        <v>3793.4</v>
+        <v>1709.25</v>
       </c>
       <c r="H10">
-        <v>3805</v>
+        <v>1712.5</v>
       </c>
       <c r="I10">
-        <v>4445.6</v>
+        <v>1861.35</v>
       </c>
       <c r="J10">
-        <v>4450</v>
+        <v>1865</v>
       </c>
       <c r="K10">
-        <v>3911.35</v>
+        <v>2116.45</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1478,575 +1452,282 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>1428.6</v>
+        <v>41.2</v>
       </c>
       <c r="C11">
-        <v>1479.4</v>
+        <v>39.08</v>
       </c>
       <c r="D11">
-        <v>1482</v>
+        <v>39.15</v>
       </c>
       <c r="E11">
-        <v>1628.15</v>
+        <v>44.05</v>
       </c>
       <c r="F11">
-        <v>1632.1</v>
+        <v>44.12</v>
       </c>
       <c r="G11">
-        <v>1709.25</v>
+        <v>50.45</v>
       </c>
       <c r="H11">
-        <v>1712.5</v>
+        <v>50.6</v>
       </c>
       <c r="I11">
-        <v>1861.35</v>
+        <v>60.48</v>
       </c>
       <c r="J11">
-        <v>1865</v>
+        <v>60.75</v>
       </c>
       <c r="K11">
-        <v>2116.45</v>
+        <v>103.95</v>
       </c>
     </row>
-    <row r="12" ht="23.4" spans="1:11">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
+      <c r="B12">
+        <v>350.57</v>
+      </c>
+      <c r="C12">
+        <v>339.58</v>
+      </c>
+      <c r="D12">
+        <v>339.7</v>
+      </c>
+      <c r="E12">
+        <v>336.56</v>
+      </c>
+      <c r="F12">
+        <v>337.19</v>
+      </c>
+      <c r="G12">
+        <v>325.06</v>
+      </c>
+      <c r="H12">
+        <v>327.01</v>
+      </c>
+      <c r="I12">
+        <v>369.59</v>
+      </c>
+      <c r="J12">
+        <v>370.92</v>
+      </c>
+      <c r="K12">
+        <v>435.52</v>
+      </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>11</v>
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <v>327.53</v>
+      </c>
+      <c r="C13">
+        <v>327.44</v>
+      </c>
+      <c r="D13">
+        <v>328.74</v>
+      </c>
+      <c r="E13">
+        <v>334.99</v>
+      </c>
+      <c r="F13">
+        <v>338.99</v>
+      </c>
+      <c r="G13">
+        <v>322.35</v>
+      </c>
+      <c r="H13">
+        <v>321.75</v>
+      </c>
+      <c r="I13">
+        <v>363.02</v>
+      </c>
+      <c r="J13">
+        <v>361.34</v>
+      </c>
+      <c r="K13">
+        <v>481.2</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14">
-        <v>41.2</v>
+        <v>42.01</v>
       </c>
       <c r="C14">
-        <v>39.08</v>
+        <v>54.97</v>
       </c>
       <c r="D14">
-        <v>39.15</v>
+        <v>55.68</v>
       </c>
       <c r="E14">
-        <v>44.05</v>
+        <v>66.04</v>
       </c>
       <c r="F14">
-        <v>44.12</v>
+        <v>66.91</v>
       </c>
       <c r="G14">
-        <v>50.45</v>
+        <v>69.06</v>
       </c>
       <c r="H14">
-        <v>50.6</v>
+        <v>69.61</v>
       </c>
       <c r="I14">
-        <v>60.48</v>
+        <v>60</v>
       </c>
       <c r="J14">
-        <v>60.75</v>
+        <v>60.23</v>
       </c>
       <c r="K14">
-        <v>103.95</v>
+        <v>62.21</v>
       </c>
     </row>
-    <row r="15" ht="23.4" spans="1:11">
-      <c r="A15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
+        <v>117.57</v>
+      </c>
+      <c r="C15">
+        <v>146.04</v>
+      </c>
+      <c r="D15">
+        <v>147.46</v>
+      </c>
+      <c r="E15">
+        <v>139.99</v>
+      </c>
+      <c r="F15">
+        <v>141.49</v>
+      </c>
+      <c r="G15">
+        <v>129.63</v>
+      </c>
+      <c r="H15">
+        <v>130.6</v>
+      </c>
+      <c r="I15">
+        <v>143.05</v>
+      </c>
+      <c r="J15">
+        <v>143.05</v>
+      </c>
+      <c r="K15">
+        <v>166.25</v>
+      </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>11</v>
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
+        <v>1205</v>
+      </c>
+      <c r="C16">
+        <v>1248</v>
+      </c>
+      <c r="D16">
+        <v>1245</v>
+      </c>
+      <c r="E16">
+        <v>1180</v>
+      </c>
+      <c r="F16">
+        <v>1175</v>
+      </c>
+      <c r="G16">
+        <v>1120</v>
+      </c>
+      <c r="H16">
+        <v>1118</v>
+      </c>
+      <c r="I16">
+        <v>1095</v>
+      </c>
+      <c r="J16">
+        <v>1092</v>
+      </c>
+      <c r="K16">
+        <v>1105</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B17">
-        <v>350.57</v>
+        <v>1085</v>
       </c>
       <c r="C17">
-        <v>339.58</v>
+        <v>1120</v>
       </c>
       <c r="D17">
-        <v>339.7</v>
+        <v>1118</v>
       </c>
       <c r="E17">
-        <v>336.56</v>
+        <v>1065</v>
       </c>
       <c r="F17">
-        <v>337.19</v>
+        <v>1060</v>
       </c>
       <c r="G17">
-        <v>325.06</v>
+        <v>1045</v>
       </c>
       <c r="H17">
-        <v>327.01</v>
+        <v>1048</v>
       </c>
       <c r="I17">
-        <v>369.59</v>
+        <v>1145</v>
       </c>
       <c r="J17">
-        <v>370.92</v>
+        <v>1150</v>
       </c>
       <c r="K17">
-        <v>435.52</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B18">
-        <v>327.53</v>
+        <v>13994</v>
       </c>
       <c r="C18">
-        <v>327.44</v>
+        <v>17354</v>
       </c>
       <c r="D18">
-        <v>328.74</v>
+        <v>17387</v>
       </c>
       <c r="E18">
-        <v>334.99</v>
+        <v>18105</v>
       </c>
       <c r="F18">
-        <v>338.99</v>
+        <v>18131</v>
       </c>
       <c r="G18">
-        <v>322.35</v>
+        <v>21731</v>
       </c>
       <c r="H18">
-        <v>321.75</v>
+        <v>21727</v>
       </c>
       <c r="I18">
-        <v>363.02</v>
+        <v>23645</v>
       </c>
       <c r="J18">
-        <v>361.34</v>
+        <v>23600</v>
       </c>
       <c r="K18">
-        <v>481.2</v>
-      </c>
-    </row>
-    <row r="19" ht="23.4" spans="1:11">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21">
-        <v>42.01</v>
-      </c>
-      <c r="C21">
-        <v>54.97</v>
-      </c>
-      <c r="D21">
-        <v>55.68</v>
-      </c>
-      <c r="E21">
-        <v>66.04</v>
-      </c>
-      <c r="F21">
-        <v>66.91</v>
-      </c>
-      <c r="G21">
-        <v>69.06</v>
-      </c>
-      <c r="H21">
-        <v>69.61</v>
-      </c>
-      <c r="I21">
-        <v>60</v>
-      </c>
-      <c r="J21">
-        <v>60.23</v>
-      </c>
-      <c r="K21">
-        <v>62.21</v>
-      </c>
-    </row>
-    <row r="22" ht="23.4" spans="1:11">
-      <c r="A22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24">
-        <v>117.57</v>
-      </c>
-      <c r="C24">
-        <v>146.04</v>
-      </c>
-      <c r="D24">
-        <v>147.46</v>
-      </c>
-      <c r="E24">
-        <v>139.99</v>
-      </c>
-      <c r="F24">
-        <v>141.49</v>
-      </c>
-      <c r="G24">
-        <v>129.63</v>
-      </c>
-      <c r="H24">
-        <v>130.6</v>
-      </c>
-      <c r="I24">
-        <v>143.05</v>
-      </c>
-      <c r="J24">
-        <v>143.05</v>
-      </c>
-      <c r="K24">
-        <v>166.25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25">
-        <v>1205</v>
-      </c>
-      <c r="C25">
-        <v>1248</v>
-      </c>
-      <c r="D25">
-        <v>1245</v>
-      </c>
-      <c r="E25">
-        <v>1180</v>
-      </c>
-      <c r="F25">
-        <v>1175</v>
-      </c>
-      <c r="G25">
-        <v>1120</v>
-      </c>
-      <c r="H25">
-        <v>1118</v>
-      </c>
-      <c r="I25">
-        <v>1095</v>
-      </c>
-      <c r="J25">
-        <v>1092</v>
-      </c>
-      <c r="K25">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26">
-        <v>1085</v>
-      </c>
-      <c r="C26">
-        <v>1120</v>
-      </c>
-      <c r="D26">
-        <v>1118</v>
-      </c>
-      <c r="E26">
-        <v>1065</v>
-      </c>
-      <c r="F26">
-        <v>1060</v>
-      </c>
-      <c r="G26">
-        <v>1045</v>
-      </c>
-      <c r="H26">
-        <v>1048</v>
-      </c>
-      <c r="I26">
-        <v>1145</v>
-      </c>
-      <c r="J26">
-        <v>1150</v>
-      </c>
-      <c r="K26">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="27" ht="23.4" spans="1:11">
-      <c r="A27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29">
-        <v>13994</v>
-      </c>
-      <c r="C29">
-        <v>17354</v>
-      </c>
-      <c r="D29">
-        <v>17387</v>
-      </c>
-      <c r="E29">
-        <v>18105</v>
-      </c>
-      <c r="F29">
-        <v>18131</v>
-      </c>
-      <c r="G29">
-        <v>21731</v>
-      </c>
-      <c r="H29">
-        <v>21727</v>
-      </c>
-      <c r="I29">
-        <v>23645</v>
-      </c>
-      <c r="J29">
-        <v>23600</v>
-      </c>
-      <c r="K29">
         <v>26130</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A27:K27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
